--- a/Dev_GNC/TableData/StagePresetDataTable.xlsx
+++ b/Dev_GNC/TableData/StagePresetDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5125874D-71F3-4381-99B7-7E24E3544741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FDD7CE-3620-417F-A5C4-C08F89DF535D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{51E4D770-A38F-4EAA-BA83-FF11107A8864}"/>
   </bookViews>
@@ -74,103 +74,103 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_1_1.TMP_1_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_1_2.TMP_1_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_1_3.TMP_1_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_1_4.TMP_1_4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_1_5.TMP_1_5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_2_1.TMP_2_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_3_1.TMP_3_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_4_1.TMP_4_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_5_1.TMP_5_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_3_2.TMP_3_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_2_2.TMP_2_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_4_2.TMP_4_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_5_2.TMP_5_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_2_3.TMP_2_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_2_4.TMP_2_4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_2_5.TMP_2_5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_3_3.TMP_3_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_3_4.TMP_3_4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_3_5.TMP_3_5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_4_3.TMP_4_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_4_4.TMP_4_4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_4_5.TMP_4_5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_5_3.TMP_5_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_5_4.TMP_5_4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Variant_CardGame/DataTables/TileMap/TMP_5_5.TMP_5_5</t>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_1_1.TMP_1_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_2_1.TMP_2_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_3_1.TMP_3_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_4_1.TMP_4_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_5_1.TMP_5_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_1_2.TMP_1_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_2_2.TMP_2_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_3_2.TMP_3_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_4_2.TMP_4_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_5_2.TMP_5_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_1_3.TMP_1_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_2_3.TMP_2_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_3_3.TMP_3_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_4_3.TMP_4_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_5_3.TMP_5_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_1_4.TMP_1_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_2_4.TMP_2_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_3_4.TMP_3_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_4_4.TMP_4_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_5_4.TMP_5_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_1_5.TMP_1_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_2_5.TMP_2_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_3_5.TMP_3_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_4_5.TMP_4_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/CardGame/DataTables/TileMap/TMP_5_5.TMP_5_5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -598,16 +598,16 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -621,19 +621,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -647,19 +647,19 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
         <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -673,19 +673,19 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -699,16 +699,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>
